--- a/artfynd/A 22347-2026 artfynd.xlsx
+++ b/artfynd/A 22347-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6963,6 +6963,1210 @@
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133571959</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>634096</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6662803</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133571937</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101338</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>634045</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6663099</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133571935</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>633968</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6663034</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133571958</v>
+      </c>
+      <c r="B65" t="n">
+        <v>75433</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>634096</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6662805</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>133571951</v>
+      </c>
+      <c r="B66" t="n">
+        <v>75433</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>634104</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6662940</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>133571936</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>634015</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6663102</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>133571939</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101338</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>634044</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6663096</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133571961</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>634076</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6662669</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>133571966</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>634030</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6662583</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>133571941</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97370</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>53</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>634034</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6663018</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133571949</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>634066</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6662973</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22347-2026 artfynd.xlsx
+++ b/artfynd/A 22347-2026 artfynd.xlsx
@@ -7393,45 +7393,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133571951</v>
+        <v>133571936</v>
       </c>
       <c r="B66" t="n">
-        <v>75433</v>
+        <v>99130</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>634104</v>
+        <v>634015</v>
       </c>
       <c r="R66" t="n">
-        <v>6662940</v>
+        <v>6663102</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7463,7 +7472,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7473,7 +7482,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7500,54 +7509,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133571936</v>
+        <v>133571951</v>
       </c>
       <c r="B67" t="n">
-        <v>99130</v>
+        <v>75433</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>634015</v>
+        <v>634104</v>
       </c>
       <c r="R67" t="n">
-        <v>6663102</v>
+        <v>6662940</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7955,10 +7955,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133571941</v>
+        <v>133571949</v>
       </c>
       <c r="B71" t="n">
-        <v>97370</v>
+        <v>57955</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7966,21 +7966,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>634034</v>
+        <v>634066</v>
       </c>
       <c r="R71" t="n">
-        <v>6663018</v>
+        <v>6662973</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8062,10 +8062,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133571949</v>
+        <v>133571941</v>
       </c>
       <c r="B72" t="n">
-        <v>57955</v>
+        <v>97370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8073,21 +8073,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>634066</v>
+        <v>634034</v>
       </c>
       <c r="R72" t="n">
-        <v>6662973</v>
+        <v>6663018</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 22347-2026 artfynd.xlsx
+++ b/artfynd/A 22347-2026 artfynd.xlsx
@@ -7393,54 +7393,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133571936</v>
+        <v>133571951</v>
       </c>
       <c r="B66" t="n">
-        <v>99130</v>
+        <v>75433</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>634015</v>
+        <v>634104</v>
       </c>
       <c r="R66" t="n">
-        <v>6663102</v>
+        <v>6662940</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7472,7 +7463,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7482,7 +7473,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7509,45 +7500,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133571951</v>
+        <v>133571936</v>
       </c>
       <c r="B67" t="n">
-        <v>75433</v>
+        <v>99130</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>634104</v>
+        <v>634015</v>
       </c>
       <c r="R67" t="n">
-        <v>6662940</v>
+        <v>6663102</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7955,10 +7955,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133571949</v>
+        <v>133571941</v>
       </c>
       <c r="B71" t="n">
-        <v>57955</v>
+        <v>97370</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7966,21 +7966,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>634066</v>
+        <v>634034</v>
       </c>
       <c r="R71" t="n">
-        <v>6662973</v>
+        <v>6663018</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8062,10 +8062,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133571941</v>
+        <v>133571949</v>
       </c>
       <c r="B72" t="n">
-        <v>97370</v>
+        <v>57955</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8073,21 +8073,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>634034</v>
+        <v>634066</v>
       </c>
       <c r="R72" t="n">
-        <v>6663018</v>
+        <v>6662973</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 22347-2026 artfynd.xlsx
+++ b/artfynd/A 22347-2026 artfynd.xlsx
@@ -7723,7 +7723,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133571961</v>
+        <v>133571966</v>
       </c>
       <c r="B69" t="n">
         <v>99181</v>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>634076</v>
+        <v>634030</v>
       </c>
       <c r="R69" t="n">
-        <v>6662669</v>
+        <v>6662583</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7839,7 +7839,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133571966</v>
+        <v>133571961</v>
       </c>
       <c r="B70" t="n">
         <v>99181</v>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>634030</v>
+        <v>634076</v>
       </c>
       <c r="R70" t="n">
-        <v>6662583</v>
+        <v>6662669</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7955,10 +7955,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133571941</v>
+        <v>133571949</v>
       </c>
       <c r="B71" t="n">
-        <v>97421</v>
+        <v>57972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7966,21 +7966,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>634034</v>
+        <v>634066</v>
       </c>
       <c r="R71" t="n">
-        <v>6663018</v>
+        <v>6662973</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8062,10 +8062,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133571949</v>
+        <v>133571941</v>
       </c>
       <c r="B72" t="n">
-        <v>57972</v>
+        <v>97421</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8073,21 +8073,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>634066</v>
+        <v>634034</v>
       </c>
       <c r="R72" t="n">
-        <v>6662973</v>
+        <v>6663018</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 22347-2026 artfynd.xlsx
+++ b/artfynd/A 22347-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132039427</v>
+        <v>132039425</v>
       </c>
       <c r="B2" t="n">
-        <v>96554</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634057</v>
+        <v>634034</v>
       </c>
       <c r="R2" t="n">
-        <v>6662980</v>
+        <v>6663005</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132047474</v>
+        <v>132039439</v>
       </c>
       <c r="B3" t="n">
-        <v>75428</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634083</v>
+        <v>634099</v>
       </c>
       <c r="R3" t="n">
-        <v>6662868</v>
+        <v>6662755</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +850,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132039461</v>
+        <v>132039440</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634019</v>
+        <v>634102</v>
       </c>
       <c r="R4" t="n">
-        <v>6662594</v>
+        <v>6662748</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +999,7 @@
         <v>132039464</v>
       </c>
       <c r="B5" t="n">
-        <v>97358</v>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132039460</v>
+        <v>132039471</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>97435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634034</v>
+        <v>634063</v>
       </c>
       <c r="R6" t="n">
-        <v>6662584</v>
+        <v>6662830</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1163,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132039481</v>
+        <v>132039476</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>97435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634045</v>
+        <v>634019</v>
       </c>
       <c r="R7" t="n">
-        <v>6662998</v>
+        <v>6662926</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1270,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132039470</v>
+        <v>132039478</v>
       </c>
       <c r="B8" t="n">
-        <v>91929</v>
+        <v>97435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,19 +1328,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1338,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634060</v>
+        <v>634011</v>
       </c>
       <c r="R8" t="n">
-        <v>6662776</v>
+        <v>6662937</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1373,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132039482</v>
+        <v>132047461</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>97435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,37 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633998</v>
+        <v>634017</v>
       </c>
       <c r="R9" t="n">
-        <v>6663013</v>
+        <v>6662940</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,24 +1492,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,22 +1509,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132039478</v>
+        <v>132047462</v>
       </c>
       <c r="B10" t="n">
-        <v>97358</v>
+        <v>97435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,17 +1552,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634011</v>
+        <v>633997</v>
       </c>
       <c r="R10" t="n">
-        <v>6662937</v>
+        <v>6662597</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,19 +1589,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,44 +1606,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132047471</v>
+        <v>132047463</v>
       </c>
       <c r="B11" t="n">
-        <v>75428</v>
+        <v>97435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634056</v>
+        <v>634084</v>
       </c>
       <c r="R11" t="n">
-        <v>6662736</v>
+        <v>6662908</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1726,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132039425</v>
+        <v>133571941</v>
       </c>
       <c r="B12" t="n">
-        <v>97358</v>
+        <v>97435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,10 +1753,10 @@
         <v>634034</v>
       </c>
       <c r="R12" t="n">
-        <v>6663005</v>
+        <v>6663018</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1791,22 +1780,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1833,48 +1822,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132047466</v>
+        <v>133571960</v>
       </c>
       <c r="B13" t="n">
-        <v>96458</v>
+        <v>97435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634081</v>
+        <v>634108</v>
       </c>
       <c r="R13" t="n">
-        <v>6662733</v>
+        <v>6662742</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,12 +1887,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,44 +1917,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132039448</v>
+        <v>132039427</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>96629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1965,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634024</v>
+        <v>634057</v>
       </c>
       <c r="R14" t="n">
-        <v>6662585</v>
+        <v>6662980</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2000,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2010,12 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132039449</v>
+        <v>132230444</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>96629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,37 +2047,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634019</v>
+        <v>633998</v>
       </c>
       <c r="R15" t="n">
-        <v>6662585</v>
+        <v>6662610</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2107,22 +2113,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,28 +2127,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132039433</v>
+        <v>132230445</v>
       </c>
       <c r="B16" t="n">
-        <v>75428</v>
+        <v>96629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,37 +2157,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634103</v>
+        <v>634018</v>
       </c>
       <c r="R16" t="n">
-        <v>6662786</v>
+        <v>6663031</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2214,22 +2223,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,50 +2237,51 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132039428</v>
+        <v>132039462</v>
       </c>
       <c r="B17" t="n">
-        <v>75428</v>
+        <v>83350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634050</v>
+        <v>634032</v>
       </c>
       <c r="R17" t="n">
-        <v>6662931</v>
+        <v>6662656</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132047462</v>
+        <v>132047484</v>
       </c>
       <c r="B18" t="n">
-        <v>97358</v>
+        <v>83350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,21 +2374,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633997</v>
+        <v>634038</v>
       </c>
       <c r="R18" t="n">
-        <v>6662597</v>
+        <v>6662654</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132039462</v>
+        <v>132039468</v>
       </c>
       <c r="B19" t="n">
-        <v>83299</v>
+        <v>96535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,34 +2471,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634032</v>
+        <v>634064</v>
       </c>
       <c r="R19" t="n">
-        <v>6662656</v>
+        <v>6662762</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2530,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2549,6 +2553,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2567,48 +2572,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132039467</v>
+        <v>132047467</v>
       </c>
       <c r="B20" t="n">
-        <v>75428</v>
+        <v>96535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>634072</v>
       </c>
       <c r="R20" t="n">
-        <v>6662738</v>
+        <v>6662767</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2635,71 +2644,62 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132039447</v>
+        <v>132039480</v>
       </c>
       <c r="B21" t="n">
-        <v>75428</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634029</v>
+        <v>634045</v>
       </c>
       <c r="R21" t="n">
-        <v>6662580</v>
+        <v>6662998</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039480</v>
+        <v>132047464</v>
       </c>
       <c r="B22" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,17 +2812,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>634045</v>
+        <v>634050</v>
       </c>
       <c r="R22" t="n">
-        <v>6662998</v>
+        <v>6663000</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2849,19 +2849,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2876,44 +2866,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039476</v>
+        <v>133571964</v>
       </c>
       <c r="B23" t="n">
-        <v>97358</v>
+        <v>96676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,13 +2913,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>634019</v>
+        <v>634020</v>
       </c>
       <c r="R23" t="n">
-        <v>6662926</v>
+        <v>6662582</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2953,22 +2943,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2995,10 +2985,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132039437</v>
+        <v>133571938</v>
       </c>
       <c r="B24" t="n">
-        <v>75428</v>
+        <v>96410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,21 +2996,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>2812</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3030,13 +3020,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>634108</v>
+        <v>634045</v>
       </c>
       <c r="R24" t="n">
-        <v>6662768</v>
+        <v>6663099</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3060,22 +3050,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3102,10 +3092,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132039459</v>
+        <v>132047465</v>
       </c>
       <c r="B25" t="n">
-        <v>75428</v>
+        <v>96533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,37 +3103,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634045</v>
+        <v>634021</v>
       </c>
       <c r="R25" t="n">
-        <v>6662589</v>
+        <v>6662610</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3170,19 +3160,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,22 +3177,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132039458</v>
+        <v>132047466</v>
       </c>
       <c r="B26" t="n">
-        <v>5199</v>
+        <v>96533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,37 +3200,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>634042</v>
+        <v>634081</v>
       </c>
       <c r="R26" t="n">
-        <v>6662605</v>
+        <v>6662733</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3277,19 +3257,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3304,22 +3274,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132047469</v>
+        <v>133571945</v>
       </c>
       <c r="B27" t="n">
-        <v>75428</v>
+        <v>96533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,37 +3297,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>634020</v>
+        <v>634064</v>
       </c>
       <c r="R27" t="n">
-        <v>6662596</v>
+        <v>6662985</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3381,12 +3351,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,22 +3381,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132039463</v>
+        <v>132039472</v>
       </c>
       <c r="B28" t="n">
-        <v>83290</v>
+        <v>91937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3424,21 +3404,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3448,10 +3428,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634032</v>
+        <v>634029</v>
       </c>
       <c r="R28" t="n">
-        <v>6662656</v>
+        <v>6662867</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3483,7 +3463,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3493,7 +3473,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3520,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132047464</v>
+        <v>132039428</v>
       </c>
       <c r="B29" t="n">
-        <v>91909</v>
+        <v>75468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,37 +3511,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
         <v>634050</v>
       </c>
       <c r="R29" t="n">
-        <v>6663000</v>
+        <v>6662931</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,9 +3568,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3605,22 +3595,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132039471</v>
+        <v>132039433</v>
       </c>
       <c r="B30" t="n">
-        <v>97358</v>
+        <v>75468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3628,21 +3618,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3652,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634063</v>
+        <v>634103</v>
       </c>
       <c r="R30" t="n">
-        <v>6662830</v>
+        <v>6662786</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3687,7 +3677,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3697,7 +3687,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3724,10 +3714,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132039453</v>
+        <v>132039435</v>
       </c>
       <c r="B31" t="n">
-        <v>57950</v>
+        <v>75468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,21 +3725,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3759,13 +3749,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>634000</v>
+        <v>634102</v>
       </c>
       <c r="R31" t="n">
-        <v>6662604</v>
+        <v>6662780</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3794,7 +3784,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3804,12 +3794,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3836,14 +3821,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132039456</v>
+        <v>132039436</v>
       </c>
       <c r="B32" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3871,13 +3856,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>634037</v>
+        <v>634107</v>
       </c>
       <c r="R32" t="n">
-        <v>6662606</v>
+        <v>6662773</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3906,7 +3891,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3916,7 +3901,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3943,14 +3928,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132047472</v>
+        <v>132039437</v>
       </c>
       <c r="B33" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3974,17 +3959,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>634101</v>
+        <v>634108</v>
       </c>
       <c r="R33" t="n">
-        <v>6662784</v>
+        <v>6662768</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4011,9 +3996,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4028,26 +4023,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132039451</v>
+        <v>132039444</v>
       </c>
       <c r="B34" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4075,13 +4070,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>634007</v>
+        <v>634042</v>
       </c>
       <c r="R34" t="n">
-        <v>6662592</v>
+        <v>6662585</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4110,7 +4105,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4120,7 +4115,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4147,48 +4142,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132047485</v>
+        <v>132039445</v>
       </c>
       <c r="B35" t="n">
-        <v>5179</v>
+        <v>75468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>634079</v>
+        <v>634041</v>
       </c>
       <c r="R35" t="n">
-        <v>6662720</v>
+        <v>6662588</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4215,9 +4210,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4232,60 +4237,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132047475</v>
+        <v>132039447</v>
       </c>
       <c r="B36" t="n">
-        <v>83290</v>
+        <v>75468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6439</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>634041</v>
+        <v>634029</v>
       </c>
       <c r="R36" t="n">
-        <v>6662655</v>
+        <v>6662580</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4312,9 +4317,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4329,22 +4344,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132047461</v>
+        <v>132039451</v>
       </c>
       <c r="B37" t="n">
-        <v>97358</v>
+        <v>75468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,37 +4367,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>634017</v>
+        <v>634007</v>
       </c>
       <c r="R37" t="n">
-        <v>6662940</v>
+        <v>6662592</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4409,9 +4424,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4426,22 +4451,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132047484</v>
+        <v>132039452</v>
       </c>
       <c r="B38" t="n">
-        <v>83299</v>
+        <v>75468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,37 +4474,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634038</v>
+        <v>633999</v>
       </c>
       <c r="R38" t="n">
-        <v>6662654</v>
+        <v>6662592</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4506,9 +4531,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4523,60 +4558,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132047465</v>
+        <v>132039455</v>
       </c>
       <c r="B39" t="n">
-        <v>96458</v>
+        <v>75468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634021</v>
+        <v>634020</v>
       </c>
       <c r="R39" t="n">
-        <v>6662610</v>
+        <v>6662606</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4603,9 +4638,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4620,26 +4665,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132039452</v>
+        <v>132039456</v>
       </c>
       <c r="B40" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4667,10 +4712,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633999</v>
+        <v>634037</v>
       </c>
       <c r="R40" t="n">
-        <v>6662592</v>
+        <v>6662606</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4702,7 +4747,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4712,7 +4757,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4739,48 +4784,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132047468</v>
+        <v>132039459</v>
       </c>
       <c r="B41" t="n">
-        <v>97983</v>
+        <v>75468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634099</v>
+        <v>634045</v>
       </c>
       <c r="R41" t="n">
-        <v>6662776</v>
+        <v>6662589</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4807,9 +4852,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4824,68 +4879,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132048076</v>
+        <v>132039467</v>
       </c>
       <c r="B42" t="n">
-        <v>58327</v>
+        <v>75468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>634051</v>
+        <v>634072</v>
       </c>
       <c r="R42" t="n">
-        <v>6662877</v>
+        <v>6662738</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4912,9 +4959,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4929,60 +4986,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132039472</v>
+        <v>132047469</v>
       </c>
       <c r="B43" t="n">
-        <v>91872</v>
+        <v>75468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>634029</v>
+        <v>634020</v>
       </c>
       <c r="R43" t="n">
-        <v>6662867</v>
+        <v>6662596</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5009,19 +5066,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5036,26 +5083,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132039455</v>
+        <v>132047471</v>
       </c>
       <c r="B44" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5079,17 +5126,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>634020</v>
+        <v>634056</v>
       </c>
       <c r="R44" t="n">
-        <v>6662606</v>
+        <v>6662736</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5116,19 +5163,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5143,26 +5180,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132039444</v>
+        <v>132047472</v>
       </c>
       <c r="B45" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5186,17 +5223,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>634042</v>
+        <v>634101</v>
       </c>
       <c r="R45" t="n">
-        <v>6662585</v>
+        <v>6662784</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5223,19 +5260,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5250,22 +5277,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132039477</v>
+        <v>132047473</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>75468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5273,37 +5300,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634017</v>
+        <v>634107</v>
       </c>
       <c r="R46" t="n">
-        <v>6662929</v>
+        <v>6662777</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5330,24 +5357,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5362,26 +5374,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132039445</v>
+        <v>132047474</v>
       </c>
       <c r="B47" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5405,17 +5417,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634041</v>
+        <v>634083</v>
       </c>
       <c r="R47" t="n">
-        <v>6662588</v>
+        <v>6662868</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5442,19 +5454,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5469,60 +5471,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132047477</v>
+        <v>133571951</v>
       </c>
       <c r="B48" t="n">
-        <v>4781</v>
+        <v>75468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>634094</v>
+        <v>634104</v>
       </c>
       <c r="R48" t="n">
-        <v>6662815</v>
+        <v>6662940</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5546,12 +5548,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5566,44 +5578,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132039450</v>
+        <v>133571955</v>
       </c>
       <c r="B49" t="n">
-        <v>5199</v>
+        <v>75468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5613,13 +5625,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>634019</v>
+        <v>634116</v>
       </c>
       <c r="R49" t="n">
-        <v>6662585</v>
+        <v>6662937</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5643,22 +5655,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5685,32 +5697,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132039465</v>
+        <v>133571958</v>
       </c>
       <c r="B50" t="n">
-        <v>5179</v>
+        <v>75468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5720,13 +5732,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>634064</v>
+        <v>634096</v>
       </c>
       <c r="R50" t="n">
-        <v>6662721</v>
+        <v>6662805</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5750,22 +5762,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5792,14 +5804,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132039435</v>
+        <v>133571969</v>
       </c>
       <c r="B51" t="n">
-        <v>75428</v>
+        <v>75468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5827,13 +5839,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>634102</v>
+        <v>634073</v>
       </c>
       <c r="R51" t="n">
-        <v>6662780</v>
+        <v>6662584</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5857,22 +5869,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5899,49 +5911,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132047467</v>
+        <v>132230446</v>
       </c>
       <c r="B52" t="n">
-        <v>96463</v>
+        <v>75354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>771</v>
+        <v>6427</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>634072</v>
+        <v>634006</v>
       </c>
       <c r="R52" t="n">
-        <v>6662767</v>
+        <v>6662615</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5968,12 +5976,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5982,7 +5990,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6001,49 +6008,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132039468</v>
+        <v>132039463</v>
       </c>
       <c r="B53" t="n">
-        <v>96464</v>
+        <v>83341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>771</v>
+        <v>6439</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>634064</v>
+        <v>634032</v>
       </c>
       <c r="R53" t="n">
-        <v>6662762</v>
+        <v>6662656</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6075,7 +6078,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6085,7 +6088,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6094,7 +6097,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6113,49 +6115,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230440</v>
+        <v>132047475</v>
       </c>
       <c r="B54" t="n">
-        <v>99122</v>
+        <v>83341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>634075</v>
+        <v>634041</v>
       </c>
       <c r="R54" t="n">
-        <v>6662675</v>
+        <v>6662655</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6182,17 +6180,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6201,7 +6194,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6220,10 +6212,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230444</v>
+        <v>132039448</v>
       </c>
       <c r="B55" t="n">
-        <v>96558</v>
+        <v>57972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,49 +6223,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>633998</v>
+        <v>634024</v>
       </c>
       <c r="R55" t="n">
-        <v>6662610</v>
+        <v>6662585</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6297,12 +6277,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6311,71 +6306,66 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132230442</v>
+        <v>132039453</v>
       </c>
       <c r="B56" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>634038</v>
+        <v>634000</v>
       </c>
       <c r="R56" t="n">
-        <v>6662583</v>
+        <v>6662604</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6399,17 +6389,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>6 bladrosetter</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6418,71 +6418,66 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132230441</v>
+        <v>132039477</v>
       </c>
       <c r="B57" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>634063</v>
+        <v>634017</v>
       </c>
       <c r="R57" t="n">
-        <v>6662665</v>
+        <v>6662929</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6506,17 +6501,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>mer än 10 bladrosetter</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6525,29 +6530,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132230447</v>
+        <v>132039482</v>
       </c>
       <c r="B58" t="n">
-        <v>101330</v>
+        <v>57972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6555,37 +6559,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>634012</v>
+        <v>633998</v>
       </c>
       <c r="R58" t="n">
-        <v>6663028</v>
+        <v>6663013</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6609,12 +6613,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6629,64 +6648,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132230439</v>
+        <v>133571949</v>
       </c>
       <c r="B59" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>633972</v>
+        <v>634066</v>
       </c>
       <c r="R59" t="n">
-        <v>6663034</v>
+        <v>6662973</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6710,17 +6725,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6729,29 +6749,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132230445</v>
+        <v>132039449</v>
       </c>
       <c r="B60" t="n">
-        <v>96558</v>
+        <v>5181</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6759,49 +6778,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>634018</v>
+        <v>634019</v>
       </c>
       <c r="R60" t="n">
-        <v>6663031</v>
+        <v>6662585</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6825,12 +6832,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6839,71 +6856,66 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132230443</v>
+        <v>132039461</v>
       </c>
       <c r="B61" t="n">
-        <v>99122</v>
+        <v>5181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>634048</v>
+        <v>634019</v>
       </c>
       <c r="R61" t="n">
-        <v>6662952</v>
+        <v>6662594</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6927,17 +6939,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ett fåtal bladrosetter</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6946,29 +6963,28 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133571959</v>
+        <v>132039465</v>
       </c>
       <c r="B62" t="n">
-        <v>4782</v>
+        <v>5181</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6976,21 +6992,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7000,13 +7016,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>634096</v>
+        <v>634064</v>
       </c>
       <c r="R62" t="n">
-        <v>6662803</v>
+        <v>6662721</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7030,22 +7046,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7072,10 +7088,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133571937</v>
+        <v>132039481</v>
       </c>
       <c r="B63" t="n">
-        <v>101389</v>
+        <v>5181</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7083,21 +7099,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7110,10 +7126,10 @@
         <v>634045</v>
       </c>
       <c r="R63" t="n">
-        <v>6663099</v>
+        <v>6662998</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7137,22 +7153,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7179,48 +7195,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133571935</v>
+        <v>132047485</v>
       </c>
       <c r="B64" t="n">
-        <v>99181</v>
+        <v>5181</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>633968</v>
+        <v>634079</v>
       </c>
       <c r="R64" t="n">
-        <v>6663034</v>
+        <v>6662720</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7244,22 +7260,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7274,22 +7280,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133571958</v>
+        <v>133571944</v>
       </c>
       <c r="B65" t="n">
-        <v>75454</v>
+        <v>5181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7297,21 +7303,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7321,10 +7327,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>634096</v>
+        <v>634050</v>
       </c>
       <c r="R65" t="n">
-        <v>6662805</v>
+        <v>6663008</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7356,7 +7362,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7366,7 +7372,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7393,10 +7399,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133571951</v>
+        <v>132047477</v>
       </c>
       <c r="B66" t="n">
-        <v>75454</v>
+        <v>4782</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7404,37 +7410,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>634104</v>
+        <v>634094</v>
       </c>
       <c r="R66" t="n">
-        <v>6662940</v>
+        <v>6662815</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7458,22 +7464,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7488,66 +7484,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133571936</v>
+        <v>133571959</v>
       </c>
       <c r="B67" t="n">
-        <v>99181</v>
+        <v>4782</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>634015</v>
+        <v>634096</v>
       </c>
       <c r="R67" t="n">
-        <v>6663102</v>
+        <v>6662803</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7579,7 +7566,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7589,7 +7576,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7616,10 +7603,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133571939</v>
+        <v>132048076</v>
       </c>
       <c r="B68" t="n">
-        <v>101389</v>
+        <v>58349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7627,37 +7614,45 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>634044</v>
+        <v>634051</v>
       </c>
       <c r="R68" t="n">
-        <v>6663096</v>
+        <v>6662877</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7681,22 +7676,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7711,69 +7696,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133571966</v>
+        <v>132039450</v>
       </c>
       <c r="B69" t="n">
-        <v>99181</v>
+        <v>5201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>634030</v>
+        <v>634019</v>
       </c>
       <c r="R69" t="n">
-        <v>6662583</v>
+        <v>6662585</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7797,22 +7773,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7839,57 +7815,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133571961</v>
+        <v>132039458</v>
       </c>
       <c r="B70" t="n">
-        <v>99181</v>
+        <v>5201</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>634076</v>
+        <v>634042</v>
       </c>
       <c r="R70" t="n">
-        <v>6662669</v>
+        <v>6662605</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7913,22 +7880,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7955,27 +7922,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133571949</v>
+        <v>133571947</v>
       </c>
       <c r="B71" t="n">
-        <v>57972</v>
+        <v>5201</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7990,10 +7957,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>634066</v>
+        <v>634064</v>
       </c>
       <c r="R71" t="n">
-        <v>6662973</v>
+        <v>6662985</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8025,7 +7992,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8035,7 +8002,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8062,32 +8029,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133571941</v>
+        <v>132039460</v>
       </c>
       <c r="B72" t="n">
-        <v>97421</v>
+        <v>8449</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8100,10 +8067,10 @@
         <v>634034</v>
       </c>
       <c r="R72" t="n">
-        <v>6663018</v>
+        <v>6662584</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8127,22 +8094,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8166,6 +8133,1520 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132230439</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tvigölingen, ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>633972</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6663034</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132230440</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tvigölingen, ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>634075</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6662675</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132230441</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tvigölingen, ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>634063</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6662665</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>mer än 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132230442</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tvigölingen, ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>634038</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6662583</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132230443</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tvigölingen, ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>634048</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6662952</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ett fåtal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133571935</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>633968</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6663034</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133571936</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>634015</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6663102</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>133571961</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>634076</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6662669</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>133571962</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>634066</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6662632</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>133571966</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>634030</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6662583</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132047468</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Tvigölingen, ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>634099</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6662776</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132230447</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Tvigölingen, ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>634012</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6663028</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>133571937</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>634045</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6663099</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>133571939</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Tvigölingen Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>634044</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6663096</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
